--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/report-schema/memberProgressReportSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/report-schema/memberProgressReportSchema-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="101">
-  <si>
-    <t>Statement: memberProgressReportSchema – validate query parameters for member progress report.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="96">
+  <si>
+    <t>Statement: memberProgressReportSchema – Validates query parameters for a member progress report using Zod safeParse. Returns { success: true, data } when all required fields are present and satisfy their constraints. Returns { success: false, error } with a path pointing to the offending field when any constraint is violated. memberId is required (at least 1 character, not whitespace-only). startDate is required and must be in YYYY-MM-DD format. endDate is required and must be in YYYY-MM-DD format. The schema does not enforce date ordering; startDate equal to or after endDate is accepted.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: MemberProgressReportInput { memberId, startDate, endDate }</t>
+    <t>Input: MemberProgressReportInput { memberId: string, startDate: string, endDate: string }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>memberId non-empty | YYYY-MM-DD format for dates</t>
+    <t>Input is passed directly to memberProgressReportSchema.safeParse(). memberId: required, at least 1 character, not whitespace-only. startDate: required, YYYY-MM-DD format. endDate: required, YYYY-MM-DD format. Date ordering is not enforced; startDate may equal or exceed endDate.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: { success: boolean, data?, error? }</t>
+    <t>Output: { success: boolean, data?: MemberProgressReportInput, error?: ZodError }</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Validation results match constraints.</t>
+    <t>On success: parsed data contains the supplied fields matching the input. On failure: error.issues[0].path contains the name of the offending field.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -67,55 +67,55 @@
     <t>All fields valid</t>
   </si>
   <si>
-    <t>All fields correct</t>
-  </si>
-  <si>
-    <t>MemberId presence</t>
-  </si>
-  <si>
-    <t>Present</t>
-  </si>
-  <si>
-    <t>Missing</t>
-  </si>
-  <si>
-    <t>StartDate presence</t>
-  </si>
-  <si>
-    <t>EndDate presence</t>
-  </si>
-  <si>
-    <t>MemberId value</t>
-  </si>
-  <si>
-    <t>Non-whitespace</t>
-  </si>
-  <si>
-    <t>Whitespace only</t>
-  </si>
-  <si>
-    <t>StartDate format</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t>Invalid format</t>
-  </si>
-  <si>
-    <t>EndDate format</t>
-  </si>
-  <si>
-    <t>Same day range</t>
-  </si>
-  <si>
-    <t>Start == End</t>
-  </si>
-  <si>
-    <t>Reverse range</t>
-  </si>
-  <si>
-    <t>Start &gt; End (Allowed)</t>
+    <t>All required fields present with valid values → success: true, parsed data matches the input</t>
+  </si>
+  <si>
+    <t>memberId presence</t>
+  </si>
+  <si>
+    <t>memberId field absent → success: false, error path contains "memberId"</t>
+  </si>
+  <si>
+    <t>startDate presence</t>
+  </si>
+  <si>
+    <t>startDate field absent → success: false, error path contains "startDate"</t>
+  </si>
+  <si>
+    <t>endDate presence</t>
+  </si>
+  <si>
+    <t>endDate field absent → success: false, error path contains "endDate"</t>
+  </si>
+  <si>
+    <t>memberId value</t>
+  </si>
+  <si>
+    <t>memberId: "   " (whitespace-only) → success: false, error path contains "memberId"</t>
+  </si>
+  <si>
+    <t>startDate format</t>
+  </si>
+  <si>
+    <t>startDate: "2024-01-01" (valid YYYY-MM-DD) → success: true</t>
+  </si>
+  <si>
+    <t>startDate: "01/01/2024" (MM/DD/YYYY, wrong format) → success: false, error path contains "startDate"</t>
+  </si>
+  <si>
+    <t>endDate format</t>
+  </si>
+  <si>
+    <t>endDate: "2024-01-31" (valid YYYY-MM-DD) → success: true</t>
+  </si>
+  <si>
+    <t>endDate: "2024.12.31" (dot-separated, wrong format) → success: false, error path contains "endDate"</t>
+  </si>
+  <si>
+    <t>date range ordering</t>
+  </si>
+  <si>
+    <t>startDate equals endDate ("2024-01-01" == "2024-01-01") → success: true; startDate after endDate ("2024-06-01" &gt; "2024-01-01") → success: true (ordering not enforced)</t>
   </si>
   <si>
     <t>No TC</t>
@@ -136,10 +136,10 @@
     <t>EC-1</t>
   </si>
   <si>
-    <t>Valid query params</t>
-  </si>
-  <si>
-    <t>success: true</t>
+    <t>all required fields provided with valid values: memberId "member-123", startDate "2024-01-01", endDate "2024-01-31"</t>
+  </si>
+  <si>
+    <t>success: true, parsed data matches the input</t>
   </si>
   <si>
     <t>Passed</t>
@@ -148,52 +148,61 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>Missing memberId</t>
-  </si>
-  <si>
-    <t>success: false</t>
+    <t>query with memberId field absent</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "memberId"</t>
   </si>
   <si>
     <t>EC-3</t>
   </si>
   <si>
-    <t>Missing startDate</t>
+    <t>query with startDate field absent</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "startDate"</t>
   </si>
   <si>
     <t>EC-4</t>
   </si>
   <si>
-    <t>Missing endDate</t>
+    <t>query with endDate field absent</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "endDate"</t>
   </si>
   <si>
     <t>EC-5</t>
   </si>
   <si>
-    <t>memberId="   " (Spaces)</t>
+    <t>valid query with memberId: "   " (whitespace-only)</t>
   </si>
   <si>
     <t>EC-6</t>
   </si>
   <si>
-    <t>startDate="01/01/2024"</t>
+    <t>valid query with startDate: "01/01/2024" (MM/DD/YYYY, wrong format)</t>
   </si>
   <si>
     <t>EC-7</t>
   </si>
   <si>
-    <t>endDate="2024.12.31"</t>
+    <t>valid query with endDate: "2024.12.31" (dot-separated, wrong format)</t>
   </si>
   <si>
     <t>EC-8</t>
   </si>
   <si>
-    <t>startDate == endDate</t>
-  </si>
-  <si>
-    <t>EC-9</t>
-  </si>
-  <si>
-    <t>startDate &gt; endDate</t>
+    <t>valid query with startDate: "2024-01-01" and endDate: "2024-01-01" (same day)</t>
+  </si>
+  <si>
+    <t>success: true, parsed startDate is "2024-01-01" and endDate is "2024-01-01"</t>
+  </si>
+  <si>
+    <t>valid query with startDate: "2024-06-01" and endDate: "2024-01-01" (startDate after endDate)</t>
+  </si>
+  <si>
+    <t>success: true, parsed startDate is "2024-06-01" and endDate is "2024-01-01"</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -202,37 +211,43 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>MemberId length</t>
-  </si>
-  <si>
-    <t>0 chars (Below Min)</t>
-  </si>
-  <si>
-    <t>1 char (At Min)</t>
-  </si>
-  <si>
-    <t>2 chars (Above Min)</t>
+    <t>memberId length</t>
+  </si>
+  <si>
+    <t>memberId: "" (length 0, min - 1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>memberId: "A" (length 1, min): at minimum → success: true, parsed memberId is "A"</t>
+  </si>
+  <si>
+    <t>memberId: "AB" (length 2, min + 1): above minimum → success: true, parsed memberId is "AB"</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 MemId 0ch</t>
-  </si>
-  <si>
-    <t>memberId=""</t>
-  </si>
-  <si>
-    <t>BVA-1 MemId 1ch</t>
-  </si>
-  <si>
-    <t>memberId="A"</t>
-  </si>
-  <si>
-    <t>BVA-1 MemId 2ch</t>
-  </si>
-  <si>
-    <t>memberId="AB"</t>
+    <t>BVA-1 (memberId=0)</t>
+  </si>
+  <si>
+    <t>valid query with memberId: "" (0 characters)</t>
+  </si>
+  <si>
+    <t>BVA-2 (memberId=1)</t>
+  </si>
+  <si>
+    <t>valid query with memberId: "A" (1 character)</t>
+  </si>
+  <si>
+    <t>success: true, parsed memberId is "A"</t>
+  </si>
+  <si>
+    <t>BVA-3 (memberId=2)</t>
+  </si>
+  <si>
+    <t>valid query with memberId: "AB" (2 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed memberId is "AB"</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -241,43 +256,13 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Valid query parameters</t>
-  </si>
-  <si>
-    <t>MemberId field missing</t>
-  </si>
-  <si>
-    <t>StartDate field missing</t>
-  </si>
-  <si>
-    <t>EndDate field missing</t>
-  </si>
-  <si>
-    <t>MemberId whitespace "   "</t>
-  </si>
-  <si>
-    <t>StartDate format wrong</t>
-  </si>
-  <si>
-    <t>EndDate format wrong</t>
-  </si>
-  <si>
-    <t>Same day range (Start == End)</t>
-  </si>
-  <si>
-    <t>Reverse range (Start &gt; End)</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>memberId empty ""</t>
-  </si>
-  <si>
-    <t>memberId length 1</t>
-  </si>
-  <si>
-    <t>memberId length 2</t>
+    <t>BVA-2</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
   </si>
   <si>
     <t>Testing</t>
@@ -310,7 +295,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>RPT-01</t>
+    <t>SCHEMA-13</t>
   </si>
   <si>
     <t>n/a</t>
@@ -835,7 +820,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -879,10 +864,10 @@
         <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -890,13 +875,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -907,10 +892,10 @@
         <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -918,10 +903,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>24</v>
@@ -949,10 +934,10 @@
         <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -960,26 +945,12 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1063,7 +1034,7 @@
         <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>41</v>
@@ -1074,13 +1045,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>41</v>
@@ -1091,10 +1062,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>44</v>
@@ -1108,13 +1079,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>41</v>
@@ -1125,13 +1096,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>41</v>
@@ -1142,13 +1113,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>41</v>
@@ -1162,10 +1133,10 @@
         <v>57</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>41</v>
@@ -1189,13 +1160,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1203,32 +1174,32 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+      <c r="A3" s="1">
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
+      <c r="A4" s="1">
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1254,7 +1225,7 @@
         <v>33</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>35</v>
@@ -1271,10 +1242,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>44</v>
@@ -1288,13 +1259,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>41</v>
@@ -1305,13 +1276,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>41</v>
@@ -1341,10 +1312,10 @@
         <v>33</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>35</v>
@@ -1367,7 +1338,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>40</v>
@@ -1387,7 +1358,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>44</v>
@@ -1407,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>41</v>
@@ -1421,16 +1392,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>41</v>
@@ -1441,13 +1412,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>44</v>
@@ -1461,16 +1432,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>41</v>
@@ -1481,16 +1452,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>41</v>
@@ -1501,16 +1472,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>41</v>
@@ -1527,10 +1498,10 @@
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>41</v>
@@ -1544,10 +1515,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>44</v>
@@ -1564,13 +1535,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>41</v>
@@ -1584,13 +1555,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>41</v>
@@ -1621,16 +1592,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1638,39 +1609,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B3" s="1">
         <v>12</v>
@@ -1685,19 +1656,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/report-schema/memberProgressReportSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/report-schema/memberProgressReportSchema-bbt-form.xlsx
@@ -295,7 +295,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-13</t>
+    <t>SCHEMA-15</t>
   </si>
   <si>
     <t>n/a</t>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/report-schema/memberProgressReportSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/report-schema/memberProgressReportSchema-bbt-form.xlsx
@@ -295,7 +295,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-15</t>
+    <t>SCHEMA-17</t>
   </si>
   <si>
     <t>n/a</t>
